--- a/FM-MN-07_CUTTER GRINDING-01.xlsx
+++ b/FM-MN-07_CUTTER GRINDING-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD761B2A-1ED7-4DAA-9592-192637444C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FF30E6-D48C-489B-946C-5B67F0AC5B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,9 +403,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -445,6 +442,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1501,80 +1501,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="24" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+      <c r="Y1" s="24"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="24"/>
+      <c r="AB1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="24"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="24"/>
     </row>
     <row r="2" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="24" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
     </row>
     <row r="3" spans="1:33" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="19"/>
@@ -1612,49 +1612,49 @@
       <c r="AG3" s="17"/>
     </row>
     <row r="4" spans="1:33" s="12" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="35"/>
-      <c r="AC4" s="35"/>
-      <c r="AD4" s="35"/>
-      <c r="AE4" s="35"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4" s="36"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="34"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="34"/>
+      <c r="AE4" s="34"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="35"/>
     </row>
     <row r="5" spans="1:33" s="12" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="23"/>
-      <c r="B5" s="38"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="13">
         <v>1</v>
       </c>
@@ -2017,139 +2017,139 @@
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="26"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="26"/>
-      <c r="V13" s="26"/>
-      <c r="W13" s="26"/>
-      <c r="X13" s="26"/>
-      <c r="Y13" s="26"/>
-      <c r="Z13" s="26"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
-      <c r="AC13" s="26"/>
-      <c r="AD13" s="26"/>
-      <c r="AE13" s="26"/>
-      <c r="AF13" s="26"/>
-      <c r="AG13" s="26"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="33"/>
+      <c r="AB13" s="33"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="B14" s="5"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
+      <c r="AE14" s="22"/>
+      <c r="AF14" s="22"/>
+      <c r="AG14" s="22"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="5"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="27"/>
-      <c r="AB15" s="27"/>
-      <c r="AC15" s="22"/>
-      <c r="AD15" s="22"/>
-      <c r="AE15" s="22"/>
-      <c r="AF15" s="22"/>
-      <c r="AG15" s="22"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="21"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="21"/>
+      <c r="AA15" s="26"/>
+      <c r="AB15" s="26"/>
+      <c r="AC15" s="21"/>
+      <c r="AD15" s="21"/>
+      <c r="AE15" s="21"/>
+      <c r="AF15" s="21"/>
+      <c r="AG15" s="21"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="5"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="23"/>
-      <c r="AA16" s="23"/>
-      <c r="AB16" s="23"/>
-      <c r="AC16" s="23"/>
-      <c r="AD16" s="23"/>
-      <c r="AE16" s="23"/>
-      <c r="AF16" s="23"/>
-      <c r="AG16" s="23"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="22"/>
+      <c r="AF16" s="22"/>
+      <c r="AG16" s="22"/>
     </row>
     <row r="17" spans="2:33" ht="19.5" customHeight="1">
       <c r="B17" s="20" t="s">
@@ -2157,25 +2157,56 @@
       </c>
     </row>
     <row r="18" spans="2:33" ht="321" customHeight="1">
-      <c r="B18" s="21"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="38"/>
+      <c r="W18" s="38"/>
+      <c r="X18" s="38"/>
+      <c r="Y18" s="38"/>
+      <c r="Z18" s="38"/>
+      <c r="AA18" s="38"/>
+      <c r="AB18" s="38"/>
+      <c r="AC18" s="38"/>
+      <c r="AD18" s="38"/>
+      <c r="AE18" s="38"/>
+      <c r="AF18" s="38"/>
+      <c r="AG18" s="38"/>
     </row>
     <row r="19" spans="2:33" ht="21" customHeight="1">
       <c r="AA19" s="4"/>
       <c r="AB19" s="4"/>
-      <c r="AC19" s="32"/>
-      <c r="AD19" s="33"/>
-      <c r="AE19" s="33"/>
-      <c r="AF19" s="33"/>
-      <c r="AG19" s="33"/>
+      <c r="AC19" s="31"/>
+      <c r="AD19" s="32"/>
+      <c r="AE19" s="32"/>
+      <c r="AF19" s="32"/>
+      <c r="AG19" s="32"/>
     </row>
     <row r="20" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC20" s="29" t="s">
+      <c r="AC20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="AD20" s="30"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="29"/>
+      <c r="AF20" s="29"/>
+      <c r="AG20" s="29"/>
     </row>
     <row r="21" spans="2:33" ht="14.25" customHeight="1">
       <c r="C21" s="3"/>
@@ -2184,7 +2215,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="71">
+    <mergeCell ref="B18:AG18"/>
     <mergeCell ref="C4:AG4"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="Z15:Z16"/>

--- a/FM-MN-07_CUTTER GRINDING-01.xlsx
+++ b/FM-MN-07_CUTTER GRINDING-01.xlsx
@@ -1760,8 +1760,16 @@
       <c r="AB6" s="13" t="n"/>
       <c r="AC6" s="13" t="n"/>
       <c r="AD6" s="13" t="n"/>
-      <c r="AE6" s="13" t="n"/>
-      <c r="AF6" s="13" t="n"/>
+      <c r="AE6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="13" t="n"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -1801,8 +1809,16 @@
       <c r="AB7" s="13" t="n"/>
       <c r="AC7" s="13" t="n"/>
       <c r="AD7" s="13" t="n"/>
-      <c r="AE7" s="13" t="n"/>
-      <c r="AF7" s="13" t="n"/>
+      <c r="AE7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="13" t="n"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -1842,8 +1858,16 @@
       <c r="AB8" s="13" t="n"/>
       <c r="AC8" s="13" t="n"/>
       <c r="AD8" s="13" t="n"/>
-      <c r="AE8" s="13" t="n"/>
-      <c r="AF8" s="13" t="n"/>
+      <c r="AE8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG8" s="13" t="n"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -1883,8 +1907,16 @@
       <c r="AB9" s="13" t="n"/>
       <c r="AC9" s="13" t="n"/>
       <c r="AD9" s="13" t="n"/>
-      <c r="AE9" s="13" t="n"/>
-      <c r="AF9" s="13" t="n"/>
+      <c r="AE9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="13" t="n"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -1924,8 +1956,16 @@
       <c r="AB10" s="13" t="n"/>
       <c r="AC10" s="13" t="n"/>
       <c r="AD10" s="13" t="n"/>
-      <c r="AE10" s="13" t="n"/>
-      <c r="AF10" s="13" t="n"/>
+      <c r="AE10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="13" t="n"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -2029,8 +2069,16 @@
       <c r="AB13" s="33" t="n"/>
       <c r="AC13" s="25" t="n"/>
       <c r="AD13" s="25" t="n"/>
-      <c r="AE13" s="25" t="n"/>
-      <c r="AF13" s="25" t="n"/>
+      <c r="AE13" s="33" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
+      <c r="AF13" s="33" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="AG13" s="25" t="n"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -2143,7 +2191,7 @@
       </c>
     </row>
     <row r="18" ht="321" customHeight="1">
-      <c r="B18" s="38" t="n"/>
+      <c r="B18" s="38" t="inlineStr"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="AA19" s="4" t="n"/>

--- a/FM-MN-07_CUTTER GRINDING-01.xlsx
+++ b/FM-MN-07_CUTTER GRINDING-01.xlsx
@@ -328,7 +328,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -421,6 +421,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1732,45 +1735,37 @@
           <t>การ WORM UP แกน Y พร้อมใช้งาน</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="13" t="n"/>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="13" t="n"/>
-      <c r="U6" s="13" t="n"/>
-      <c r="V6" s="13" t="n"/>
-      <c r="W6" s="13" t="n"/>
-      <c r="X6" s="13" t="n"/>
-      <c r="Y6" s="13" t="n"/>
-      <c r="Z6" s="13" t="n"/>
-      <c r="AA6" s="13" t="n"/>
-      <c r="AB6" s="13" t="n"/>
-      <c r="AC6" s="13" t="n"/>
-      <c r="AD6" s="13" t="n"/>
-      <c r="AE6" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="13" t="n"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr"/>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr"/>
+      <c r="M6" s="13" t="inlineStr"/>
+      <c r="N6" s="13" t="inlineStr"/>
+      <c r="O6" s="13" t="inlineStr"/>
+      <c r="P6" s="13" t="inlineStr"/>
+      <c r="Q6" s="13" t="inlineStr"/>
+      <c r="R6" s="13" t="inlineStr"/>
+      <c r="S6" s="13" t="inlineStr"/>
+      <c r="T6" s="13" t="inlineStr"/>
+      <c r="U6" s="13" t="inlineStr"/>
+      <c r="V6" s="13" t="inlineStr"/>
+      <c r="W6" s="13" t="inlineStr"/>
+      <c r="X6" s="13" t="inlineStr"/>
+      <c r="Y6" s="13" t="inlineStr"/>
+      <c r="Z6" s="13" t="inlineStr"/>
+      <c r="AA6" s="13" t="inlineStr"/>
+      <c r="AB6" s="13" t="inlineStr"/>
+      <c r="AC6" s="13" t="inlineStr"/>
+      <c r="AD6" s="13" t="inlineStr"/>
+      <c r="AE6" s="13" t="inlineStr"/>
+      <c r="AF6" s="13" t="inlineStr"/>
+      <c r="AG6" s="13" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A7" s="11" t="n">
@@ -1781,45 +1776,37 @@
           <t>การ WORM UP แกน Z พร้อมใช้งาน</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="13" t="n"/>
-      <c r="P7" s="13" t="n"/>
-      <c r="Q7" s="13" t="n"/>
-      <c r="R7" s="13" t="n"/>
-      <c r="S7" s="13" t="n"/>
-      <c r="T7" s="13" t="n"/>
-      <c r="U7" s="13" t="n"/>
-      <c r="V7" s="13" t="n"/>
-      <c r="W7" s="13" t="n"/>
-      <c r="X7" s="13" t="n"/>
-      <c r="Y7" s="13" t="n"/>
-      <c r="Z7" s="13" t="n"/>
-      <c r="AA7" s="13" t="n"/>
-      <c r="AB7" s="13" t="n"/>
-      <c r="AC7" s="13" t="n"/>
-      <c r="AD7" s="13" t="n"/>
-      <c r="AE7" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="13" t="n"/>
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
+      <c r="M7" s="13" t="inlineStr"/>
+      <c r="N7" s="13" t="inlineStr"/>
+      <c r="O7" s="13" t="inlineStr"/>
+      <c r="P7" s="13" t="inlineStr"/>
+      <c r="Q7" s="13" t="inlineStr"/>
+      <c r="R7" s="13" t="inlineStr"/>
+      <c r="S7" s="13" t="inlineStr"/>
+      <c r="T7" s="13" t="inlineStr"/>
+      <c r="U7" s="13" t="inlineStr"/>
+      <c r="V7" s="13" t="inlineStr"/>
+      <c r="W7" s="13" t="inlineStr"/>
+      <c r="X7" s="13" t="inlineStr"/>
+      <c r="Y7" s="13" t="inlineStr"/>
+      <c r="Z7" s="13" t="inlineStr"/>
+      <c r="AA7" s="13" t="inlineStr"/>
+      <c r="AB7" s="13" t="inlineStr"/>
+      <c r="AC7" s="13" t="inlineStr"/>
+      <c r="AD7" s="13" t="inlineStr"/>
+      <c r="AE7" s="13" t="inlineStr"/>
+      <c r="AF7" s="13" t="inlineStr"/>
+      <c r="AG7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A8" s="11" t="n">
@@ -1830,45 +1817,37 @@
           <t>ตรวจสอบการทำงานของไฟฟ้าและแสงสว่าง</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="13" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="13" t="n"/>
-      <c r="S8" s="13" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="13" t="n"/>
-      <c r="V8" s="13" t="n"/>
-      <c r="W8" s="13" t="n"/>
-      <c r="X8" s="13" t="n"/>
-      <c r="Y8" s="13" t="n"/>
-      <c r="Z8" s="13" t="n"/>
-      <c r="AA8" s="13" t="n"/>
-      <c r="AB8" s="13" t="n"/>
-      <c r="AC8" s="13" t="n"/>
-      <c r="AD8" s="13" t="n"/>
-      <c r="AE8" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG8" s="13" t="n"/>
+      <c r="C8" s="13" t="inlineStr"/>
+      <c r="D8" s="13" t="inlineStr"/>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="13" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
+      <c r="M8" s="13" t="inlineStr"/>
+      <c r="N8" s="13" t="inlineStr"/>
+      <c r="O8" s="13" t="inlineStr"/>
+      <c r="P8" s="13" t="inlineStr"/>
+      <c r="Q8" s="13" t="inlineStr"/>
+      <c r="R8" s="13" t="inlineStr"/>
+      <c r="S8" s="13" t="inlineStr"/>
+      <c r="T8" s="13" t="inlineStr"/>
+      <c r="U8" s="13" t="inlineStr"/>
+      <c r="V8" s="13" t="inlineStr"/>
+      <c r="W8" s="13" t="inlineStr"/>
+      <c r="X8" s="13" t="inlineStr"/>
+      <c r="Y8" s="13" t="inlineStr"/>
+      <c r="Z8" s="13" t="inlineStr"/>
+      <c r="AA8" s="13" t="inlineStr"/>
+      <c r="AB8" s="13" t="inlineStr"/>
+      <c r="AC8" s="13" t="inlineStr"/>
+      <c r="AD8" s="13" t="inlineStr"/>
+      <c r="AE8" s="13" t="inlineStr"/>
+      <c r="AF8" s="13" t="inlineStr"/>
+      <c r="AG8" s="13" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A9" s="11" t="n">
@@ -1879,45 +1858,37 @@
           <t>ตรวจสอบการทำงานของมอเตอร์ มีการหมุนปกติ</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="13" t="n"/>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="13" t="n"/>
-      <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="13" t="n"/>
-      <c r="R9" s="13" t="n"/>
-      <c r="S9" s="13" t="n"/>
-      <c r="T9" s="13" t="n"/>
-      <c r="U9" s="13" t="n"/>
-      <c r="V9" s="13" t="n"/>
-      <c r="W9" s="13" t="n"/>
-      <c r="X9" s="13" t="n"/>
-      <c r="Y9" s="13" t="n"/>
-      <c r="Z9" s="13" t="n"/>
-      <c r="AA9" s="13" t="n"/>
-      <c r="AB9" s="13" t="n"/>
-      <c r="AC9" s="13" t="n"/>
-      <c r="AD9" s="13" t="n"/>
-      <c r="AE9" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="13" t="n"/>
+      <c r="C9" s="13" t="inlineStr"/>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="13" t="inlineStr"/>
+      <c r="N9" s="13" t="inlineStr"/>
+      <c r="O9" s="13" t="inlineStr"/>
+      <c r="P9" s="13" t="inlineStr"/>
+      <c r="Q9" s="13" t="inlineStr"/>
+      <c r="R9" s="13" t="inlineStr"/>
+      <c r="S9" s="13" t="inlineStr"/>
+      <c r="T9" s="13" t="inlineStr"/>
+      <c r="U9" s="13" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="W9" s="13" t="inlineStr"/>
+      <c r="X9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="Z9" s="13" t="inlineStr"/>
+      <c r="AA9" s="13" t="inlineStr"/>
+      <c r="AB9" s="13" t="inlineStr"/>
+      <c r="AC9" s="13" t="inlineStr"/>
+      <c r="AD9" s="13" t="inlineStr"/>
+      <c r="AE9" s="13" t="inlineStr"/>
+      <c r="AF9" s="13" t="inlineStr"/>
+      <c r="AG9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A10" s="11" t="n">
@@ -1928,45 +1899,37 @@
           <t>ตรวจสอบการจับหัวคอเรต</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="13" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="13" t="n"/>
-      <c r="U10" s="13" t="n"/>
-      <c r="V10" s="13" t="n"/>
-      <c r="W10" s="13" t="n"/>
-      <c r="X10" s="13" t="n"/>
-      <c r="Y10" s="13" t="n"/>
-      <c r="Z10" s="13" t="n"/>
-      <c r="AA10" s="13" t="n"/>
-      <c r="AB10" s="13" t="n"/>
-      <c r="AC10" s="13" t="n"/>
-      <c r="AD10" s="13" t="n"/>
-      <c r="AE10" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="13" t="n"/>
+      <c r="C10" s="13" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr"/>
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr"/>
+      <c r="M10" s="13" t="inlineStr"/>
+      <c r="N10" s="13" t="inlineStr"/>
+      <c r="O10" s="13" t="inlineStr"/>
+      <c r="P10" s="13" t="inlineStr"/>
+      <c r="Q10" s="13" t="inlineStr"/>
+      <c r="R10" s="13" t="inlineStr"/>
+      <c r="S10" s="13" t="inlineStr"/>
+      <c r="T10" s="13" t="inlineStr"/>
+      <c r="U10" s="13" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="W10" s="13" t="inlineStr"/>
+      <c r="X10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="Z10" s="13" t="inlineStr"/>
+      <c r="AA10" s="13" t="inlineStr"/>
+      <c r="AB10" s="13" t="inlineStr"/>
+      <c r="AC10" s="13" t="inlineStr"/>
+      <c r="AD10" s="13" t="inlineStr"/>
+      <c r="AE10" s="13" t="inlineStr"/>
+      <c r="AF10" s="13" t="inlineStr"/>
+      <c r="AG10" s="13" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A11" s="11" t="n"/>
@@ -2041,45 +2004,37 @@
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="25" t="n"/>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="25" t="n"/>
-      <c r="L13" s="25" t="n"/>
-      <c r="M13" s="25" t="n"/>
-      <c r="N13" s="25" t="n"/>
-      <c r="O13" s="25" t="n"/>
-      <c r="P13" s="25" t="n"/>
-      <c r="Q13" s="25" t="n"/>
-      <c r="R13" s="25" t="n"/>
-      <c r="S13" s="25" t="n"/>
-      <c r="T13" s="25" t="n"/>
-      <c r="U13" s="25" t="n"/>
-      <c r="V13" s="25" t="n"/>
-      <c r="W13" s="25" t="n"/>
-      <c r="X13" s="25" t="n"/>
-      <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="25" t="n"/>
-      <c r="AA13" s="33" t="n"/>
-      <c r="AB13" s="33" t="n"/>
-      <c r="AC13" s="25" t="n"/>
-      <c r="AD13" s="25" t="n"/>
-      <c r="AE13" s="33" t="inlineStr">
-        <is>
-          <t>ณัช วิกรัยเจริญ</t>
-        </is>
-      </c>
-      <c r="AF13" s="33" t="inlineStr">
-        <is>
-          <t>ณัช วิกรัยเจริญ</t>
-        </is>
-      </c>
-      <c r="AG13" s="25" t="n"/>
+      <c r="C13" s="25" t="inlineStr"/>
+      <c r="D13" s="25" t="inlineStr"/>
+      <c r="E13" s="25" t="inlineStr"/>
+      <c r="F13" s="25" t="inlineStr"/>
+      <c r="G13" s="25" t="inlineStr"/>
+      <c r="H13" s="25" t="inlineStr"/>
+      <c r="I13" s="25" t="inlineStr"/>
+      <c r="J13" s="25" t="inlineStr"/>
+      <c r="K13" s="25" t="inlineStr"/>
+      <c r="L13" s="25" t="inlineStr"/>
+      <c r="M13" s="25" t="inlineStr"/>
+      <c r="N13" s="25" t="inlineStr"/>
+      <c r="O13" s="25" t="inlineStr"/>
+      <c r="P13" s="25" t="inlineStr"/>
+      <c r="Q13" s="25" t="inlineStr"/>
+      <c r="R13" s="25" t="inlineStr"/>
+      <c r="S13" s="25" t="inlineStr"/>
+      <c r="T13" s="25" t="inlineStr"/>
+      <c r="U13" s="25" t="inlineStr"/>
+      <c r="V13" s="25" t="inlineStr"/>
+      <c r="W13" s="25" t="inlineStr"/>
+      <c r="X13" s="25" t="inlineStr"/>
+      <c r="Y13" s="25" t="inlineStr"/>
+      <c r="Z13" s="25" t="inlineStr"/>
+      <c r="AA13" s="33" t="inlineStr"/>
+      <c r="AB13" s="33" t="inlineStr"/>
+      <c r="AC13" s="25" t="inlineStr"/>
+      <c r="AD13" s="25" t="inlineStr"/>
+      <c r="AE13" s="33" t="inlineStr"/>
+      <c r="AF13" s="33" t="inlineStr"/>
+      <c r="AG13" s="25" t="inlineStr"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="B14" s="5" t="n"/>
@@ -2117,37 +2072,37 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="21" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="21" t="n"/>
-      <c r="P15" s="21" t="n"/>
-      <c r="Q15" s="21" t="n"/>
-      <c r="R15" s="21" t="n"/>
-      <c r="S15" s="21" t="n"/>
-      <c r="T15" s="21" t="n"/>
-      <c r="U15" s="21" t="n"/>
-      <c r="V15" s="21" t="n"/>
-      <c r="W15" s="21" t="n"/>
-      <c r="X15" s="21" t="n"/>
-      <c r="Y15" s="21" t="n"/>
-      <c r="Z15" s="21" t="n"/>
-      <c r="AA15" s="26" t="n"/>
-      <c r="AB15" s="26" t="n"/>
-      <c r="AC15" s="21" t="n"/>
-      <c r="AD15" s="21" t="n"/>
-      <c r="AE15" s="21" t="n"/>
-      <c r="AF15" s="21" t="n"/>
-      <c r="AG15" s="21" t="n"/>
+      <c r="C15" s="21" t="inlineStr"/>
+      <c r="D15" s="21" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr"/>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+      <c r="H15" s="21" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
+      <c r="K15" s="21" t="inlineStr"/>
+      <c r="L15" s="21" t="inlineStr"/>
+      <c r="M15" s="21" t="inlineStr"/>
+      <c r="N15" s="21" t="inlineStr"/>
+      <c r="O15" s="21" t="inlineStr"/>
+      <c r="P15" s="21" t="inlineStr"/>
+      <c r="Q15" s="21" t="inlineStr"/>
+      <c r="R15" s="21" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr"/>
+      <c r="T15" s="21" t="inlineStr"/>
+      <c r="U15" s="21" t="inlineStr"/>
+      <c r="V15" s="21" t="inlineStr"/>
+      <c r="W15" s="21" t="inlineStr"/>
+      <c r="X15" s="21" t="inlineStr"/>
+      <c r="Y15" s="21" t="inlineStr"/>
+      <c r="Z15" s="21" t="inlineStr"/>
+      <c r="AA15" s="26" t="inlineStr"/>
+      <c r="AB15" s="26" t="inlineStr"/>
+      <c r="AC15" s="21" t="inlineStr"/>
+      <c r="AD15" s="21" t="inlineStr"/>
+      <c r="AE15" s="21" t="inlineStr"/>
+      <c r="AF15" s="21" t="inlineStr"/>
+      <c r="AG15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="B16" s="5" t="n"/>
@@ -2191,7 +2146,7 @@
       </c>
     </row>
     <row r="18" ht="321" customHeight="1">
-      <c r="B18" s="38" t="inlineStr"/>
+      <c r="B18" s="39" t="inlineStr"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="AA19" s="4" t="n"/>

--- a/FM-MN-07_CUTTER GRINDING-01.xlsx
+++ b/FM-MN-07_CUTTER GRINDING-01.xlsx
@@ -1740,7 +1740,11 @@
       <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="13" t="inlineStr"/>
       <c r="J6" s="13" t="inlineStr"/>
       <c r="K6" s="13" t="inlineStr"/>
@@ -1781,7 +1785,11 @@
       <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="13" t="inlineStr"/>
       <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="13" t="inlineStr"/>
       <c r="J7" s="13" t="inlineStr"/>
       <c r="K7" s="13" t="inlineStr"/>
@@ -1822,7 +1830,11 @@
       <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="inlineStr"/>
       <c r="G8" s="13" t="inlineStr"/>
-      <c r="H8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="13" t="inlineStr"/>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
@@ -1863,7 +1875,11 @@
       <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr"/>
       <c r="G9" s="13" t="inlineStr"/>
-      <c r="H9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="13" t="inlineStr"/>
       <c r="J9" s="13" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr"/>
@@ -1904,7 +1920,11 @@
       <c r="E10" s="13" t="inlineStr"/>
       <c r="F10" s="13" t="inlineStr"/>
       <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="13" t="inlineStr"/>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr"/>
@@ -2009,7 +2029,11 @@
       <c r="E13" s="25" t="inlineStr"/>
       <c r="F13" s="25" t="inlineStr"/>
       <c r="G13" s="25" t="inlineStr"/>
-      <c r="H13" s="25" t="inlineStr"/>
+      <c r="H13" s="33" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="I13" s="25" t="inlineStr"/>
       <c r="J13" s="25" t="inlineStr"/>
       <c r="K13" s="25" t="inlineStr"/>

--- a/FM-MN-07_CUTTER GRINDING-01.xlsx
+++ b/FM-MN-07_CUTTER GRINDING-01.xlsx
@@ -1745,7 +1745,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="13" t="inlineStr"/>
       <c r="K6" s="13" t="inlineStr"/>
       <c r="L6" s="13" t="inlineStr"/>
@@ -1790,7 +1794,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="13" t="inlineStr"/>
       <c r="K7" s="13" t="inlineStr"/>
       <c r="L7" s="13" t="inlineStr"/>
@@ -1835,7 +1843,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
       <c r="L8" s="13" t="inlineStr"/>
@@ -1880,7 +1892,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="13" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr"/>
       <c r="L9" s="13" t="inlineStr"/>
@@ -1925,7 +1941,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr"/>
       <c r="L10" s="13" t="inlineStr"/>
@@ -2034,7 +2054,11 @@
           <t>ณัช วิกรัยเจริญ</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr"/>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="J13" s="25" t="inlineStr"/>
       <c r="K13" s="25" t="inlineStr"/>
       <c r="L13" s="25" t="inlineStr"/>

--- a/FM-MN-07_CUTTER GRINDING-01.xlsx
+++ b/FM-MN-07_CUTTER GRINDING-01.xlsx
@@ -2125,7 +2125,11 @@
       <c r="E15" s="21" t="inlineStr"/>
       <c r="F15" s="21" t="inlineStr"/>
       <c r="G15" s="21" t="inlineStr"/>
-      <c r="H15" s="21" t="inlineStr"/>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>รัชพล</t>
+        </is>
+      </c>
       <c r="I15" s="21" t="inlineStr"/>
       <c r="J15" s="21" t="inlineStr"/>
       <c r="K15" s="21" t="inlineStr"/>

--- a/FM-MN-07_CUTTER GRINDING-01.xlsx
+++ b/FM-MN-07_CUTTER GRINDING-01.xlsx
@@ -1750,7 +1750,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="13" t="inlineStr"/>
       <c r="L6" s="13" t="inlineStr"/>
       <c r="M6" s="13" t="inlineStr"/>
@@ -1799,7 +1803,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="13" t="inlineStr"/>
       <c r="L7" s="13" t="inlineStr"/>
       <c r="M7" s="13" t="inlineStr"/>
@@ -1848,7 +1856,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="13" t="inlineStr"/>
       <c r="L8" s="13" t="inlineStr"/>
       <c r="M8" s="13" t="inlineStr"/>
@@ -1897,7 +1909,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="13" t="inlineStr"/>
       <c r="L9" s="13" t="inlineStr"/>
       <c r="M9" s="13" t="inlineStr"/>
@@ -1946,7 +1962,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="13" t="inlineStr"/>
       <c r="L10" s="13" t="inlineStr"/>
       <c r="M10" s="13" t="inlineStr"/>
@@ -2059,7 +2079,11 @@
           <t>ณัช วิกรัยเจริญ</t>
         </is>
       </c>
-      <c r="J13" s="25" t="inlineStr"/>
+      <c r="J13" s="33" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="K13" s="25" t="inlineStr"/>
       <c r="L13" s="25" t="inlineStr"/>
       <c r="M13" s="25" t="inlineStr"/>

--- a/FM-MN-07_CUTTER GRINDING-01.xlsx
+++ b/FM-MN-07_CUTTER GRINDING-01.xlsx
@@ -1756,7 +1756,11 @@
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="13" t="inlineStr"/>
       <c r="N6" s="13" t="inlineStr"/>
       <c r="O6" s="13" t="inlineStr"/>
@@ -1809,7 +1813,11 @@
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr"/>
-      <c r="L7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="13" t="inlineStr"/>
       <c r="N7" s="13" t="inlineStr"/>
       <c r="O7" s="13" t="inlineStr"/>
@@ -1862,7 +1870,11 @@
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr"/>
-      <c r="L8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="13" t="inlineStr"/>
       <c r="N8" s="13" t="inlineStr"/>
       <c r="O8" s="13" t="inlineStr"/>
@@ -1915,7 +1927,11 @@
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="13" t="inlineStr"/>
       <c r="N9" s="13" t="inlineStr"/>
       <c r="O9" s="13" t="inlineStr"/>
@@ -1968,7 +1984,11 @@
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr"/>
-      <c r="L10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="13" t="inlineStr"/>
       <c r="N10" s="13" t="inlineStr"/>
       <c r="O10" s="13" t="inlineStr"/>
@@ -2085,7 +2105,11 @@
         </is>
       </c>
       <c r="K13" s="25" t="inlineStr"/>
-      <c r="L13" s="25" t="inlineStr"/>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="M13" s="25" t="inlineStr"/>
       <c r="N13" s="25" t="inlineStr"/>
       <c r="O13" s="25" t="inlineStr"/>
